--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_10-06-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_10-06-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C79299-C367-481C-A85D-DED8E659FA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A77A750-F590-419A-B7DE-377C336C8FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31980" yWindow="3480" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1950" yWindow="5355" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="381">
   <si>
     <t>SKU</t>
   </si>
@@ -829,9 +829,6 @@
     <t>£67.92</t>
   </si>
   <si>
-    <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Max retries exceeded with url: /product/725mm-celotex-pl4060-pir-insulated-plasterboard-12m-x-24m/ (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.onlineinsulation-sales.com', port=443) at 0x1e07f9441d0&gt;, 'Connection to www.onlineinsulation-sales.com timed out. (connect timeout=30)'))</t>
-  </si>
-  <si>
     <t>£81.97</t>
   </si>
   <si>
@@ -847,9 +844,6 @@
     <t>£61.61</t>
   </si>
   <si>
-    <t>Error: HTTPConnectionPool(host='localhost', port=59844): Read timed out. (read timeout=120)</t>
-  </si>
-  <si>
     <t>£69.38</t>
   </si>
   <si>
@@ -1166,6 +1160,9 @@
   </si>
   <si>
     <t>£2655.52</t>
+  </si>
+  <si>
+    <t>£63.59</t>
   </si>
 </sst>
 </file>
@@ -1628,7 +1625,7 @@
         <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -1640,7 +1637,7 @@
         <v>30</v>
       </c>
       <c r="R2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -1684,7 +1681,7 @@
         <v>39</v>
       </c>
       <c r="N3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="O3" t="s">
         <v>40</v>
@@ -1696,7 +1693,7 @@
         <v>42</v>
       </c>
       <c r="R3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1740,7 +1737,7 @@
         <v>52</v>
       </c>
       <c r="N4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="O4" t="s">
         <v>47</v>
@@ -1752,7 +1749,7 @@
         <v>54</v>
       </c>
       <c r="R4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1796,7 +1793,7 @@
         <v>64</v>
       </c>
       <c r="N5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="O5" t="s">
         <v>57</v>
@@ -1808,7 +1805,7 @@
         <v>67</v>
       </c>
       <c r="R5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1852,7 +1849,7 @@
         <v>76</v>
       </c>
       <c r="N6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="O6" t="s">
         <v>78</v>
@@ -1864,7 +1861,7 @@
         <v>80</v>
       </c>
       <c r="R6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1908,7 +1905,7 @@
         <v>88</v>
       </c>
       <c r="N7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="O7" t="s">
         <v>89</v>
@@ -1920,7 +1917,7 @@
         <v>91</v>
       </c>
       <c r="R7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1964,7 +1961,7 @@
         <v>97</v>
       </c>
       <c r="N8" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="O8" t="s">
         <v>89</v>
@@ -2020,7 +2017,7 @@
         <v>107</v>
       </c>
       <c r="N9" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="O9" t="s">
         <v>108</v>
@@ -2076,7 +2073,7 @@
         <v>120</v>
       </c>
       <c r="N10" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="O10" t="s">
         <v>121</v>
@@ -2132,7 +2129,7 @@
         <v>130</v>
       </c>
       <c r="N11" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="O11" t="s">
         <v>131</v>
@@ -2188,7 +2185,7 @@
         <v>143</v>
       </c>
       <c r="N12" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="O12" t="s">
         <v>137</v>
@@ -2244,7 +2241,7 @@
         <v>154</v>
       </c>
       <c r="N13" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="O13" t="s">
         <v>155</v>
@@ -2300,7 +2297,7 @@
         <v>168</v>
       </c>
       <c r="N14" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="O14" t="s">
         <v>169</v>
@@ -2412,7 +2409,7 @@
         <v>194</v>
       </c>
       <c r="N16" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="O16" t="s">
         <v>195</v>
@@ -2468,7 +2465,7 @@
         <v>206</v>
       </c>
       <c r="N17" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="O17" t="s">
         <v>207</v>
@@ -2524,7 +2521,7 @@
         <v>219</v>
       </c>
       <c r="N18" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="O18" t="s">
         <v>220</v>
@@ -2580,7 +2577,7 @@
         <v>233</v>
       </c>
       <c r="N19" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="O19" t="s">
         <v>234</v>
@@ -2636,7 +2633,7 @@
         <v>246</v>
       </c>
       <c r="N20" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="O20" t="s">
         <v>247</v>
@@ -2692,7 +2689,7 @@
         <v>259</v>
       </c>
       <c r="N21" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="O21" t="s">
         <v>260</v>
@@ -2730,166 +2727,166 @@
         <v>268</v>
       </c>
       <c r="H22" t="s">
+        <v>273</v>
+      </c>
+      <c r="I22" t="s">
         <v>269</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>270</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>271</v>
-      </c>
-      <c r="K22" t="s">
-        <v>272</v>
       </c>
       <c r="L22" t="s">
         <v>26</v>
       </c>
       <c r="M22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N22" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="O22" t="s">
         <v>266</v>
       </c>
       <c r="P22" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>380</v>
+      </c>
+      <c r="R22" t="s">
         <v>274</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>275</v>
-      </c>
-      <c r="R22" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>275</v>
+      </c>
+      <c r="B23" t="s">
+        <v>276</v>
+      </c>
+      <c r="C23" t="s">
         <v>277</v>
       </c>
-      <c r="B23" t="s">
+      <c r="D23" t="s">
+        <v>277</v>
+      </c>
+      <c r="E23" t="s">
+        <v>277</v>
+      </c>
+      <c r="F23" t="s">
         <v>278</v>
-      </c>
-      <c r="C23" t="s">
-        <v>279</v>
-      </c>
-      <c r="D23" t="s">
-        <v>279</v>
-      </c>
-      <c r="E23" t="s">
-        <v>279</v>
-      </c>
-      <c r="F23" t="s">
-        <v>280</v>
       </c>
       <c r="G23" t="s">
         <v>139</v>
       </c>
       <c r="H23" t="s">
+        <v>279</v>
+      </c>
+      <c r="I23" t="s">
+        <v>280</v>
+      </c>
+      <c r="J23" t="s">
         <v>281</v>
       </c>
-      <c r="I23" t="s">
+      <c r="K23" t="s">
         <v>282</v>
-      </c>
-      <c r="J23" t="s">
-        <v>283</v>
-      </c>
-      <c r="K23" t="s">
-        <v>284</v>
       </c>
       <c r="L23" t="s">
         <v>26</v>
       </c>
       <c r="M23" t="s">
+        <v>283</v>
+      </c>
+      <c r="N23" t="s">
+        <v>374</v>
+      </c>
+      <c r="O23" t="s">
+        <v>284</v>
+      </c>
+      <c r="P23" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q23" t="s">
         <v>285</v>
       </c>
-      <c r="N23" t="s">
-        <v>376</v>
-      </c>
-      <c r="O23" t="s">
+      <c r="R23" t="s">
         <v>286</v>
-      </c>
-      <c r="P23" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>287</v>
-      </c>
-      <c r="R23" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>287</v>
+      </c>
+      <c r="B24" t="s">
+        <v>288</v>
+      </c>
+      <c r="C24" t="s">
         <v>289</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D24" t="s">
+        <v>289</v>
+      </c>
+      <c r="E24" t="s">
+        <v>289</v>
+      </c>
+      <c r="F24" t="s">
         <v>290</v>
-      </c>
-      <c r="C24" t="s">
-        <v>291</v>
-      </c>
-      <c r="D24" t="s">
-        <v>291</v>
-      </c>
-      <c r="E24" t="s">
-        <v>291</v>
-      </c>
-      <c r="F24" t="s">
-        <v>292</v>
       </c>
       <c r="G24" t="s">
         <v>139</v>
       </c>
       <c r="H24" t="s">
+        <v>291</v>
+      </c>
+      <c r="I24" t="s">
+        <v>292</v>
+      </c>
+      <c r="J24" t="s">
         <v>293</v>
       </c>
-      <c r="I24" t="s">
+      <c r="K24" t="s">
         <v>294</v>
-      </c>
-      <c r="J24" t="s">
-        <v>295</v>
-      </c>
-      <c r="K24" t="s">
-        <v>296</v>
       </c>
       <c r="L24" t="s">
         <v>26</v>
       </c>
       <c r="M24" t="s">
+        <v>295</v>
+      </c>
+      <c r="N24" t="s">
+        <v>375</v>
+      </c>
+      <c r="O24" t="s">
+        <v>296</v>
+      </c>
+      <c r="P24" t="s">
         <v>297</v>
       </c>
-      <c r="N24" t="s">
-        <v>377</v>
-      </c>
-      <c r="O24" t="s">
+      <c r="Q24" t="s">
         <v>298</v>
       </c>
-      <c r="P24" t="s">
+      <c r="R24" t="s">
         <v>299</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>300</v>
-      </c>
-      <c r="R24" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>300</v>
+      </c>
+      <c r="B25" t="s">
+        <v>301</v>
+      </c>
+      <c r="C25" t="s">
         <v>302</v>
       </c>
-      <c r="B25" t="s">
-        <v>303</v>
-      </c>
-      <c r="C25" t="s">
-        <v>304</v>
-      </c>
       <c r="D25" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E25" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F25" t="s">
         <v>139</v>
@@ -2904,7 +2901,7 @@
         <v>139</v>
       </c>
       <c r="J25" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="K25" t="s">
         <v>139</v>
@@ -2913,13 +2910,13 @@
         <v>139</v>
       </c>
       <c r="M25" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="N25" t="s">
         <v>65</v>
       </c>
       <c r="O25" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="P25" t="s">
         <v>139</v>
@@ -2933,226 +2930,226 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>306</v>
+      </c>
+      <c r="B26" t="s">
+        <v>307</v>
+      </c>
+      <c r="C26" t="s">
         <v>308</v>
       </c>
-      <c r="B26" t="s">
-        <v>309</v>
-      </c>
-      <c r="C26" t="s">
-        <v>310</v>
-      </c>
       <c r="D26" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E26" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F26" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G26" t="s">
         <v>139</v>
       </c>
       <c r="H26" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="I26" t="s">
         <v>65</v>
       </c>
       <c r="J26" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="K26" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L26" t="s">
         <v>26</v>
       </c>
       <c r="M26" t="s">
+        <v>312</v>
+      </c>
+      <c r="N26" t="s">
+        <v>376</v>
+      </c>
+      <c r="O26" t="s">
+        <v>313</v>
+      </c>
+      <c r="P26" t="s">
         <v>314</v>
       </c>
-      <c r="N26" t="s">
-        <v>378</v>
-      </c>
-      <c r="O26" t="s">
+      <c r="Q26" t="s">
         <v>315</v>
       </c>
-      <c r="P26" t="s">
+      <c r="R26" t="s">
         <v>316</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>317</v>
-      </c>
-      <c r="R26" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>317</v>
+      </c>
+      <c r="B27" t="s">
+        <v>318</v>
+      </c>
+      <c r="C27" t="s">
         <v>319</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27" t="s">
+        <v>319</v>
+      </c>
+      <c r="E27" t="s">
+        <v>319</v>
+      </c>
+      <c r="F27" t="s">
         <v>320</v>
-      </c>
-      <c r="C27" t="s">
-        <v>321</v>
-      </c>
-      <c r="D27" t="s">
-        <v>321</v>
-      </c>
-      <c r="E27" t="s">
-        <v>321</v>
-      </c>
-      <c r="F27" t="s">
-        <v>322</v>
       </c>
       <c r="G27" t="s">
         <v>139</v>
       </c>
       <c r="H27" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="I27" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J27" t="s">
         <v>139</v>
       </c>
       <c r="K27" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="L27" t="s">
         <v>26</v>
       </c>
       <c r="M27" t="s">
+        <v>324</v>
+      </c>
+      <c r="N27" t="s">
+        <v>377</v>
+      </c>
+      <c r="O27" t="s">
+        <v>325</v>
+      </c>
+      <c r="P27" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q27" t="s">
         <v>326</v>
       </c>
-      <c r="N27" t="s">
-        <v>379</v>
-      </c>
-      <c r="O27" t="s">
+      <c r="R27" t="s">
         <v>327</v>
-      </c>
-      <c r="P27" t="s">
-        <v>323</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>328</v>
-      </c>
-      <c r="R27" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>328</v>
+      </c>
+      <c r="B28" t="s">
+        <v>329</v>
+      </c>
+      <c r="C28" t="s">
         <v>330</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D28" t="s">
+        <v>330</v>
+      </c>
+      <c r="E28" t="s">
+        <v>330</v>
+      </c>
+      <c r="F28" t="s">
         <v>331</v>
-      </c>
-      <c r="C28" t="s">
-        <v>332</v>
-      </c>
-      <c r="D28" t="s">
-        <v>332</v>
-      </c>
-      <c r="E28" t="s">
-        <v>332</v>
-      </c>
-      <c r="F28" t="s">
-        <v>333</v>
       </c>
       <c r="G28" t="s">
         <v>139</v>
       </c>
       <c r="H28" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="I28" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J28" t="s">
         <v>139</v>
       </c>
       <c r="K28" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="L28" t="s">
         <v>26</v>
       </c>
       <c r="M28" t="s">
+        <v>335</v>
+      </c>
+      <c r="N28" t="s">
+        <v>378</v>
+      </c>
+      <c r="O28" t="s">
+        <v>336</v>
+      </c>
+      <c r="P28" t="s">
         <v>337</v>
       </c>
-      <c r="N28" t="s">
-        <v>380</v>
-      </c>
-      <c r="O28" t="s">
+      <c r="Q28" t="s">
         <v>338</v>
       </c>
-      <c r="P28" t="s">
+      <c r="R28" t="s">
         <v>339</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>340</v>
-      </c>
-      <c r="R28" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>340</v>
+      </c>
+      <c r="B29" t="s">
+        <v>341</v>
+      </c>
+      <c r="C29" t="s">
         <v>342</v>
       </c>
-      <c r="B29" t="s">
-        <v>343</v>
-      </c>
-      <c r="C29" t="s">
-        <v>344</v>
-      </c>
       <c r="D29" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E29" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F29" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G29" t="s">
         <v>139</v>
       </c>
       <c r="H29" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I29" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J29" t="s">
         <v>139</v>
       </c>
       <c r="K29" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="L29" t="s">
         <v>139</v>
       </c>
       <c r="M29" t="s">
+        <v>346</v>
+      </c>
+      <c r="N29" t="s">
+        <v>379</v>
+      </c>
+      <c r="O29" t="s">
+        <v>347</v>
+      </c>
+      <c r="P29" t="s">
         <v>348</v>
-      </c>
-      <c r="N29" t="s">
-        <v>381</v>
-      </c>
-      <c r="O29" t="s">
-        <v>349</v>
-      </c>
-      <c r="P29" t="s">
-        <v>350</v>
       </c>
       <c r="Q29" t="s">
         <v>139</v>
       </c>
       <c r="R29" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
